--- a/2VAR_ATSBS_T2W/2var_atsbs_t2w_WALK.xlsx
+++ b/2VAR_ATSBS_T2W/2var_atsbs_t2w_WALK.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/philliao/Downloads/Code/IB-Math-IA/2VAR_ATSBS_T2W/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8626BA3-51C8-E94F-A6DB-CB134DCD169E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FCA6AAA-9C3C-924C-AE15-7252E40F3102}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="25600" windowHeight="16000" xr2:uid="{4D1AF13A-A5F1-E34F-94D2-60D62824593C}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="40">
   <si>
     <t>district_name</t>
   </si>
@@ -137,6 +137,27 @@
   <si>
     <t>Upper 95.0%</t>
   </si>
+  <si>
+    <t>Percent WALK</t>
+  </si>
+  <si>
+    <t>p50_acr_rank</t>
+  </si>
+  <si>
+    <t>Percent WALK rank</t>
+  </si>
+  <si>
+    <t>rho=</t>
+  </si>
+  <si>
+    <t>Walk percent rank</t>
+  </si>
+  <si>
+    <t>speed_acr_rank</t>
+  </si>
+  <si>
+    <t>Percent BICYCLE rank</t>
+  </si>
 </sst>
 </file>
 
@@ -226,17 +247,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -294,13 +314,8 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>Congestion Rate to Walk</a:t>
+              <a:t>ATSBS WALK</a:t>
             </a:r>
-            <a:r>
-              <a:rPr lang="en-US" baseline="0"/>
-              <a:t> Rate</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:rich>
       </c:tx>
@@ -831,11 +846,11 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>Congestion Rate to Walk</a:t>
+              <a:t>ATSBS</a:t>
             </a:r>
             <a:r>
               <a:rPr lang="en-US" baseline="0"/>
-              <a:t> Rate (Populated)</a:t>
+              <a:t> WALK (Crowded)</a:t>
             </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
@@ -1344,11 +1359,11 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>Congestion Rate to Walk</a:t>
+              <a:t>ATSBS</a:t>
             </a:r>
             <a:r>
               <a:rPr lang="en-US" baseline="0"/>
-              <a:t> Rate (Unpopulated)</a:t>
+              <a:t> WALK (Uncrowded)</a:t>
             </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
@@ -3914,7 +3929,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C79C884C-E453-6B44-ADBD-205B6FE17472}">
-  <dimension ref="A1:AO35"/>
+  <dimension ref="A1:AO49"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:40" x14ac:dyDescent="0.2">
@@ -3925,7 +3940,7 @@
         <v>5</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>0</v>
@@ -4253,7 +4268,7 @@
         <v>5</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="E18" t="s">
         <v>9</v>
@@ -4322,10 +4337,10 @@
       <c r="C20" s="3">
         <v>2.7827199999999999</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="E20" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F20" s="7"/>
+      <c r="F20" s="6"/>
       <c r="O20" s="1">
         <v>4</v>
       </c>
@@ -4335,10 +4350,10 @@
       <c r="Q20" s="3">
         <v>3.6038389999999998</v>
       </c>
-      <c r="S20" s="7" t="s">
+      <c r="S20" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="T20" s="7"/>
+      <c r="T20" s="6"/>
       <c r="AC20" s="1">
         <v>2</v>
       </c>
@@ -4348,10 +4363,10 @@
       <c r="AE20" s="3">
         <v>2.7827199999999999</v>
       </c>
-      <c r="AG20" s="7" t="s">
+      <c r="AG20" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="AH20" s="7"/>
+      <c r="AH20" s="6"/>
     </row>
     <row r="21" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
@@ -4363,10 +4378,10 @@
       <c r="C21" s="3">
         <v>3.6753770000000001</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E21" t="s">
         <v>11</v>
       </c>
-      <c r="F21" s="4">
+      <c r="F21">
         <v>0.73434213593254782</v>
       </c>
       <c r="O21" s="1">
@@ -4378,10 +4393,10 @@
       <c r="Q21" s="3">
         <v>2.7476090000000002</v>
       </c>
-      <c r="S21" s="4" t="s">
+      <c r="S21" t="s">
         <v>11</v>
       </c>
-      <c r="T21" s="4">
+      <c r="T21">
         <v>0.33569035403836361</v>
       </c>
       <c r="AC21" s="1">
@@ -4393,10 +4408,10 @@
       <c r="AE21" s="3">
         <v>4.2643740000000001</v>
       </c>
-      <c r="AG21" s="4" t="s">
+      <c r="AG21" t="s">
         <v>11</v>
       </c>
-      <c r="AH21" s="4">
+      <c r="AH21">
         <v>0.86060234107630551</v>
       </c>
     </row>
@@ -4410,10 +4425,10 @@
       <c r="C22" s="3">
         <v>3.6038389999999998</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E22" t="s">
         <v>12</v>
       </c>
-      <c r="F22" s="4">
+      <c r="F22">
         <v>0.53925837260597653</v>
       </c>
       <c r="O22" s="1">
@@ -4425,10 +4440,10 @@
       <c r="Q22" s="3">
         <v>2.3836249999999999</v>
       </c>
-      <c r="S22" s="4" t="s">
+      <c r="S22" t="s">
         <v>12</v>
       </c>
-      <c r="T22" s="4">
+      <c r="T22">
         <v>0.1126880137944019</v>
       </c>
       <c r="AC22" s="1">
@@ -4440,10 +4455,10 @@
       <c r="AE22" s="3">
         <v>2.2407919999999999</v>
       </c>
-      <c r="AG22" s="4" t="s">
+      <c r="AG22" t="s">
         <v>12</v>
       </c>
-      <c r="AH22" s="4">
+      <c r="AH22">
         <v>0.74063638946601773</v>
       </c>
     </row>
@@ -4457,10 +4472,10 @@
       <c r="C23" s="3">
         <v>4.2643740000000001</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" t="s">
         <v>13</v>
       </c>
-      <c r="F23" s="4">
+      <c r="F23">
         <v>0.4816656691817236</v>
       </c>
       <c r="O23" s="1">
@@ -4472,16 +4487,16 @@
       <c r="Q23" s="3">
         <v>2.8338070000000002</v>
       </c>
-      <c r="S23" s="4" t="s">
+      <c r="S23" t="s">
         <v>13</v>
       </c>
-      <c r="T23" s="4">
+      <c r="T23">
         <v>-0.10913998275699763</v>
       </c>
-      <c r="AG23" s="4" t="s">
+      <c r="AG23" t="s">
         <v>13</v>
       </c>
-      <c r="AH23" s="4">
+      <c r="AH23">
         <v>0.6109545841990266</v>
       </c>
     </row>
@@ -4495,10 +4510,10 @@
       <c r="C24" s="3">
         <v>2.7476090000000002</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="E24" t="s">
         <v>14</v>
       </c>
-      <c r="F24" s="4">
+      <c r="F24">
         <v>3.0852253966887112E-2</v>
       </c>
       <c r="O24" s="1">
@@ -4510,18 +4525,18 @@
       <c r="Q24" s="3">
         <v>2.4946600000000001</v>
       </c>
-      <c r="S24" s="4" t="s">
+      <c r="S24" t="s">
         <v>14</v>
       </c>
-      <c r="T24" s="4">
+      <c r="T24">
         <v>1.0249279997178852E-2</v>
       </c>
       <c r="AC24" s="1"/>
       <c r="AE24" s="3"/>
-      <c r="AG24" s="4" t="s">
+      <c r="AG24" t="s">
         <v>14</v>
       </c>
-      <c r="AH24" s="4">
+      <c r="AH24">
         <v>3.7099179648017115E-2</v>
       </c>
     </row>
@@ -4535,25 +4550,25 @@
       <c r="C25" s="3">
         <v>2.3836249999999999</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="E25" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F25" s="5">
+      <c r="F25" s="4">
         <v>10</v>
       </c>
-      <c r="S25" s="5" t="s">
+      <c r="S25" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="T25" s="5">
+      <c r="T25" s="4">
         <v>6</v>
       </c>
       <c r="AC25" s="1"/>
       <c r="AD25" s="1"/>
       <c r="AE25" s="3"/>
-      <c r="AG25" s="5" t="s">
+      <c r="AG25" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="AH25" s="5">
+      <c r="AH25" s="4">
         <v>4</v>
       </c>
     </row>
@@ -4604,448 +4619,871 @@
       <c r="C28" s="3">
         <v>2.4946600000000001</v>
       </c>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6" t="s">
+      <c r="E28" s="5"/>
+      <c r="F28" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G28" s="6" t="s">
+      <c r="G28" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="H28" s="6" t="s">
+      <c r="H28" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="I28" s="6" t="s">
+      <c r="I28" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="J28" s="6" t="s">
+      <c r="J28" s="5" t="s">
         <v>25</v>
       </c>
       <c r="O28" s="1"/>
       <c r="P28" s="1"/>
       <c r="Q28" s="3"/>
-      <c r="S28" s="6"/>
-      <c r="T28" s="6" t="s">
+      <c r="S28" s="5"/>
+      <c r="T28" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="U28" s="6" t="s">
+      <c r="U28" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="V28" s="6" t="s">
+      <c r="V28" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="W28" s="6" t="s">
+      <c r="W28" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="X28" s="6" t="s">
+      <c r="X28" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="AG28" s="6"/>
-      <c r="AH28" s="6" t="s">
+      <c r="AG28" s="5"/>
+      <c r="AH28" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AI28" s="6" t="s">
+      <c r="AI28" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="AJ28" s="6" t="s">
+      <c r="AJ28" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="AK28" s="6" t="s">
+      <c r="AK28" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="AL28" s="6" t="s">
+      <c r="AL28" s="5" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="29" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="E29" s="4" t="s">
+      <c r="E29" t="s">
         <v>17</v>
       </c>
-      <c r="F29" s="4">
+      <c r="F29">
         <v>1</v>
       </c>
-      <c r="G29" s="4">
+      <c r="G29">
         <v>8.9125756089575917E-3</v>
       </c>
-      <c r="H29" s="4">
+      <c r="H29">
         <v>8.9125756089575917E-3</v>
       </c>
-      <c r="I29" s="4">
+      <c r="I29">
         <v>9.3633106373487003</v>
       </c>
-      <c r="J29" s="8">
+      <c r="J29" s="7">
         <v>1.5583716034714271E-2</v>
       </c>
-      <c r="S29" s="4" t="s">
+      <c r="S29" t="s">
         <v>17</v>
       </c>
-      <c r="T29" s="4">
+      <c r="T29">
         <v>1</v>
       </c>
-      <c r="U29" s="4">
+      <c r="U29">
         <v>5.3363964017718744E-5</v>
       </c>
-      <c r="V29" s="4">
+      <c r="V29">
         <v>5.3363964017718744E-5</v>
       </c>
-      <c r="W29" s="4">
+      <c r="W29">
         <v>0.50799725709234844</v>
       </c>
-      <c r="X29" s="8">
+      <c r="X29" s="7">
         <v>0.51537860856571538</v>
       </c>
       <c r="AC29" s="1"/>
       <c r="AD29" s="1"/>
       <c r="AE29" s="3"/>
-      <c r="AG29" s="4" t="s">
+      <c r="AG29" t="s">
         <v>17</v>
       </c>
-      <c r="AH29" s="4">
+      <c r="AH29">
         <v>1</v>
       </c>
-      <c r="AI29" s="4">
+      <c r="AI29">
         <v>7.8605803535883069E-3</v>
       </c>
-      <c r="AJ29" s="4">
+      <c r="AJ29">
         <v>7.8605803535883069E-3</v>
       </c>
-      <c r="AK29" s="4">
+      <c r="AK29">
         <v>5.7111819807040973</v>
       </c>
-      <c r="AL29" s="8">
+      <c r="AL29" s="7">
         <v>0.13939765892369449</v>
       </c>
     </row>
     <row r="30" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="E30" s="4" t="s">
+      <c r="E30" t="s">
         <v>18</v>
       </c>
-      <c r="F30" s="4">
+      <c r="F30">
         <v>8</v>
       </c>
-      <c r="G30" s="4">
+      <c r="G30">
         <v>7.6148925986984127E-3</v>
       </c>
-      <c r="H30" s="4">
+      <c r="H30">
         <v>9.5186157483730159E-4</v>
       </c>
-      <c r="I30" s="4"/>
-      <c r="J30" s="4"/>
-      <c r="S30" s="4" t="s">
+      <c r="S30" t="s">
         <v>18</v>
       </c>
-      <c r="T30" s="4">
+      <c r="T30">
         <v>4</v>
       </c>
-      <c r="U30" s="4">
+      <c r="U30">
         <v>4.2019096184228212E-4</v>
       </c>
-      <c r="V30" s="4">
+      <c r="V30">
         <v>1.0504774046057053E-4</v>
       </c>
-      <c r="W30" s="4"/>
-      <c r="X30" s="4"/>
       <c r="AC30" s="1"/>
       <c r="AD30" s="1"/>
       <c r="AE30" s="3"/>
-      <c r="AG30" s="4" t="s">
+      <c r="AG30" t="s">
         <v>18</v>
       </c>
-      <c r="AH30" s="4">
+      <c r="AH30">
         <v>2</v>
       </c>
-      <c r="AI30" s="4">
+      <c r="AI30">
         <v>2.7526982611116948E-3</v>
       </c>
-      <c r="AJ30" s="4">
+      <c r="AJ30">
         <v>1.3763491305558474E-3</v>
       </c>
-      <c r="AK30" s="4"/>
-      <c r="AL30" s="4"/>
     </row>
     <row r="31" spans="1:38" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E31" s="5" t="s">
+      <c r="E31" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F31" s="5">
+      <c r="F31" s="4">
         <v>9</v>
       </c>
-      <c r="G31" s="5">
+      <c r="G31" s="4">
         <v>1.6527468207656004E-2</v>
       </c>
-      <c r="H31" s="5"/>
-      <c r="I31" s="5"/>
-      <c r="J31" s="5"/>
-      <c r="S31" s="5" t="s">
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
+      <c r="S31" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="T31" s="5">
+      <c r="T31" s="4">
         <v>5</v>
       </c>
-      <c r="U31" s="5">
+      <c r="U31" s="4">
         <v>4.7355492586000086E-4</v>
       </c>
-      <c r="V31" s="5"/>
-      <c r="W31" s="5"/>
-      <c r="X31" s="5"/>
-      <c r="AG31" s="5" t="s">
+      <c r="V31" s="4"/>
+      <c r="W31" s="4"/>
+      <c r="X31" s="4"/>
+      <c r="AG31" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="AH31" s="5">
+      <c r="AH31" s="4">
         <v>3</v>
       </c>
-      <c r="AI31" s="5">
+      <c r="AI31" s="4">
         <v>1.0613278614700001E-2</v>
       </c>
-      <c r="AJ31" s="5"/>
-      <c r="AK31" s="5"/>
-      <c r="AL31" s="5"/>
+      <c r="AJ31" s="4"/>
+      <c r="AK31" s="4"/>
+      <c r="AL31" s="4"/>
     </row>
     <row r="32" spans="1:38" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="33" spans="5:41" x14ac:dyDescent="0.2">
-      <c r="E33" s="6"/>
-      <c r="F33" s="6" t="s">
+    <row r="33" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="E33" s="5"/>
+      <c r="F33" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="G33" s="6" t="s">
+      <c r="G33" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H33" s="6" t="s">
+      <c r="H33" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="I33" s="6" t="s">
+      <c r="I33" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="J33" s="6" t="s">
+      <c r="J33" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="K33" s="6" t="s">
+      <c r="K33" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="L33" s="6" t="s">
+      <c r="L33" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="M33" s="6" t="s">
+      <c r="M33" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="S33" s="6"/>
-      <c r="T33" s="6" t="s">
+      <c r="S33" s="5"/>
+      <c r="T33" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="U33" s="6" t="s">
+      <c r="U33" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="V33" s="6" t="s">
+      <c r="V33" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="W33" s="6" t="s">
+      <c r="W33" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="X33" s="6" t="s">
+      <c r="X33" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="Y33" s="6" t="s">
+      <c r="Y33" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="Z33" s="6" t="s">
+      <c r="Z33" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="AA33" s="6" t="s">
+      <c r="AA33" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="AG33" s="6"/>
-      <c r="AH33" s="6" t="s">
+      <c r="AG33" s="5"/>
+      <c r="AH33" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="AI33" s="6" t="s">
+      <c r="AI33" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="AJ33" s="6" t="s">
+      <c r="AJ33" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="AK33" s="6" t="s">
+      <c r="AK33" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="AL33" s="6" t="s">
+      <c r="AL33" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="AM33" s="6" t="s">
+      <c r="AM33" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="AN33" s="6" t="s">
+      <c r="AN33" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="AO33" s="6" t="s">
+      <c r="AO33" s="5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="5:41" x14ac:dyDescent="0.2">
-      <c r="E34" s="4" t="s">
+    <row r="34" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="E34" t="s">
         <v>20</v>
       </c>
-      <c r="F34" s="4">
+      <c r="F34">
         <v>-3.0443156998151755E-2</v>
       </c>
-      <c r="G34" s="4">
+      <c r="G34">
         <v>4.408387406257349E-2</v>
       </c>
-      <c r="H34" s="4">
+      <c r="H34">
         <v>-0.69057354067703214</v>
       </c>
-      <c r="I34" s="8">
+      <c r="I34" s="7">
         <v>0.50936973350512371</v>
       </c>
-      <c r="J34" s="4">
+      <c r="J34">
         <v>-0.13210075288226594</v>
       </c>
-      <c r="K34" s="4">
+      <c r="K34">
         <v>7.1214438885962447E-2</v>
       </c>
-      <c r="L34" s="4">
+      <c r="L34">
         <v>-0.13210075288226594</v>
       </c>
-      <c r="M34" s="4">
+      <c r="M34">
         <v>7.1214438885962447E-2</v>
       </c>
-      <c r="S34" s="4" t="s">
+      <c r="S34" t="s">
         <v>20</v>
       </c>
-      <c r="T34" s="4">
+      <c r="T34">
         <v>-0.12552155259229297</v>
       </c>
-      <c r="U34" s="4">
+      <c r="U34">
         <v>2.4805137438354094E-2</v>
       </c>
-      <c r="V34" s="4">
+      <c r="V34">
         <v>-5.060304660848586</v>
       </c>
-      <c r="W34" s="8">
+      <c r="W34" s="7">
         <v>7.1790045014670702E-3</v>
       </c>
-      <c r="X34" s="4">
+      <c r="X34">
         <v>-0.19439165501676972</v>
       </c>
-      <c r="Y34" s="4">
+      <c r="Y34">
         <v>-5.6651450167816218E-2</v>
       </c>
-      <c r="Z34" s="4">
+      <c r="Z34">
         <v>-0.19439165501676972</v>
       </c>
-      <c r="AA34" s="4">
+      <c r="AA34">
         <v>-5.6651450167816218E-2</v>
       </c>
-      <c r="AG34" s="4" t="s">
+      <c r="AG34" t="s">
         <v>20</v>
       </c>
-      <c r="AH34" s="4">
+      <c r="AH34">
         <v>-2.0340016374338604E-2</v>
       </c>
-      <c r="AI34" s="4">
+      <c r="AI34">
         <v>7.3603303913028287E-2</v>
       </c>
-      <c r="AJ34" s="4">
+      <c r="AJ34">
         <v>-0.27634651290073792</v>
       </c>
-      <c r="AK34" s="8">
+      <c r="AK34" s="7">
         <v>0.80822062962858732</v>
       </c>
-      <c r="AL34" s="4">
+      <c r="AL34">
         <v>-0.33702947287430912</v>
       </c>
-      <c r="AM34" s="4">
+      <c r="AM34">
         <v>0.29634944012563191</v>
       </c>
-      <c r="AN34" s="4">
+      <c r="AN34">
         <v>-0.33702947287430912</v>
       </c>
-      <c r="AO34" s="4">
+      <c r="AO34">
         <v>0.29634944012563191</v>
       </c>
     </row>
-    <row r="35" spans="5:41" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E35" s="5" t="s">
+    <row r="35" spans="1:41" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="E35" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F35" s="4">
+        <v>-4.2154712185654974E-2</v>
+      </c>
+      <c r="G35" s="4">
+        <v>1.3776262598940422E-2</v>
+      </c>
+      <c r="H35" s="4">
+        <v>-3.059952718155738</v>
+      </c>
+      <c r="I35" s="8">
+        <v>1.5583716034714319E-2</v>
+      </c>
+      <c r="J35" s="4">
+        <v>-7.39228307064701E-2</v>
+      </c>
+      <c r="K35" s="4">
+        <v>-1.0386593664839853E-2</v>
+      </c>
+      <c r="L35" s="4">
+        <v>-7.39228307064701E-2</v>
+      </c>
+      <c r="M35" s="4">
+        <v>-1.0386593664839853E-2</v>
+      </c>
+      <c r="S35" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T35" s="4">
+        <v>-5.8942428360334665E-3</v>
+      </c>
+      <c r="U35" s="4">
+        <v>8.269844446080532E-3</v>
+      </c>
+      <c r="V35" s="4">
+        <v>-0.7127392630495033</v>
+      </c>
+      <c r="W35" s="8">
+        <v>0.51537860856571616</v>
+      </c>
+      <c r="X35" s="4">
+        <v>-2.8855011969100917E-2</v>
+      </c>
+      <c r="Y35" s="4">
+        <v>1.7066526297033983E-2</v>
+      </c>
+      <c r="Z35" s="4">
+        <v>-2.8855011969100917E-2</v>
+      </c>
+      <c r="AA35" s="4">
+        <v>1.7066526297033983E-2</v>
+      </c>
+      <c r="AG35" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F35" s="5">
-        <v>-4.2154712185654974E-2</v>
-      </c>
-      <c r="G35" s="5">
-        <v>1.3776262598940422E-2</v>
-      </c>
-      <c r="H35" s="5">
-        <v>-3.059952718155738</v>
-      </c>
-      <c r="I35" s="9">
-        <v>1.5583716034714319E-2</v>
-      </c>
-      <c r="J35" s="5">
-        <v>-7.39228307064701E-2</v>
-      </c>
-      <c r="K35" s="5">
-        <v>-1.0386593664839853E-2</v>
-      </c>
-      <c r="L35" s="5">
-        <v>-7.39228307064701E-2</v>
-      </c>
-      <c r="M35" s="5">
-        <v>-1.0386593664839853E-2</v>
-      </c>
-      <c r="S35" s="5" t="s">
+      <c r="AH35" s="4">
+        <v>-5.0557461265149616E-2</v>
+      </c>
+      <c r="AI35" s="4">
+        <v>2.1155449549088132E-2</v>
+      </c>
+      <c r="AJ35" s="4">
+        <v>-2.3898079380368831</v>
+      </c>
+      <c r="AK35" s="8">
+        <v>0.13939765892369449</v>
+      </c>
+      <c r="AL35" s="4">
+        <v>-0.14158201401661072</v>
+      </c>
+      <c r="AM35" s="4">
+        <v>4.0467091486311495E-2</v>
+      </c>
+      <c r="AN35" s="4">
+        <v>-0.14158201401661072</v>
+      </c>
+      <c r="AO35" s="4">
+        <v>4.0467091486311495E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A39" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="O39" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P39" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q39" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="R39" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="T35" s="5">
-        <v>-5.8942428360334665E-3</v>
-      </c>
-      <c r="U35" s="5">
-        <v>8.269844446080532E-3</v>
-      </c>
-      <c r="V35" s="5">
-        <v>-0.7127392630495033</v>
-      </c>
-      <c r="W35" s="9">
-        <v>0.51537860856571616</v>
-      </c>
-      <c r="X35" s="5">
-        <v>-2.8855011969100917E-2</v>
-      </c>
-      <c r="Y35" s="5">
-        <v>1.7066526297033983E-2</v>
-      </c>
-      <c r="Z35" s="5">
-        <v>-2.8855011969100917E-2</v>
-      </c>
-      <c r="AA35" s="5">
-        <v>1.7066526297033983E-2</v>
-      </c>
-      <c r="AG35" s="5" t="s">
+      <c r="S39" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC39" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD39" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE39" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AF39" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="AH35" s="5">
-        <v>-5.0557461265149616E-2</v>
-      </c>
-      <c r="AI35" s="5">
-        <v>2.1155449549088132E-2</v>
-      </c>
-      <c r="AJ35" s="5">
-        <v>-2.3898079380368831</v>
-      </c>
-      <c r="AK35" s="9">
-        <v>0.13939765892369449</v>
-      </c>
-      <c r="AL35" s="5">
-        <v>-0.14158201401661072</v>
-      </c>
-      <c r="AM35" s="5">
-        <v>4.0467091486311495E-2</v>
-      </c>
-      <c r="AN35" s="5">
-        <v>-0.14158201401661072</v>
-      </c>
-      <c r="AO35" s="5">
-        <v>4.0467091486311495E-2</v>
+      <c r="AG39" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="40" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A40" s="1">
+        <v>1</v>
+      </c>
+      <c r="B40" s="1">
+        <v>-0.20784630000000001</v>
+      </c>
+      <c r="C40">
+        <f>_xlfn.RANK.AVG(B40,B$40:B$49,1)</f>
+        <v>2</v>
+      </c>
+      <c r="D40" s="3">
+        <v>4.1795689999999999</v>
+      </c>
+      <c r="E40">
+        <f>_xlfn.RANK.AVG(D40,D$40:D$49,1)</f>
+        <v>9</v>
+      </c>
+      <c r="G40" t="s">
+        <v>36</v>
+      </c>
+      <c r="H40">
+        <f>CORREL(C40:C49,E40:E49)</f>
+        <v>-0.61212121212121207</v>
+      </c>
+      <c r="O40" s="1">
+        <v>3</v>
+      </c>
+      <c r="P40" s="1">
+        <v>-0.14957390000000001</v>
+      </c>
+      <c r="Q40">
+        <f>_xlfn.RANK.AVG(P40,P$40:P$45,1)</f>
+        <v>2</v>
+      </c>
+      <c r="R40" s="3">
+        <v>3.6753770000000001</v>
+      </c>
+      <c r="S40">
+        <f>_xlfn.RANK.AVG(R40,R$40:R$45,1)</f>
+        <v>6</v>
+      </c>
+      <c r="U40" t="s">
+        <v>36</v>
+      </c>
+      <c r="V40">
+        <f>CORREL(Q40:Q45,S40:S45)</f>
+        <v>-0.71428571428571441</v>
+      </c>
+      <c r="AC40" s="1">
+        <v>1</v>
+      </c>
+      <c r="AD40" s="1">
+        <v>-0.20784630000000001</v>
+      </c>
+      <c r="AE40">
+        <f>_xlfn.RANK.AVG(AD40, AD$40:AD$43,1)</f>
+        <v>2</v>
+      </c>
+      <c r="AF40" s="3">
+        <v>4.1795689999999999</v>
+      </c>
+      <c r="AG40">
+        <f t="shared" ref="AG40:AG43" si="0">_xlfn.RANK.AVG(AF40, AF$40:AF$43,1)</f>
+        <v>3</v>
+      </c>
+      <c r="AI40" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ40">
+        <f>CORREL(AE40:AE43,AG40:AG43)</f>
+        <v>-0.79999999999999982</v>
+      </c>
+    </row>
+    <row r="41" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A41" s="1">
+        <v>2</v>
+      </c>
+      <c r="B41" s="1">
+        <v>-0.13281899999999999</v>
+      </c>
+      <c r="C41">
+        <f t="shared" ref="C41:C49" si="1">_xlfn.RANK.AVG(B41,B$40:B$49,1)</f>
+        <v>9</v>
+      </c>
+      <c r="D41" s="3">
+        <v>2.7827199999999999</v>
+      </c>
+      <c r="E41">
+        <f t="shared" ref="E41:E49" si="2">_xlfn.RANK.AVG(D41,D$40:D$49,1)</f>
+        <v>5</v>
+      </c>
+      <c r="O41" s="1">
+        <v>4</v>
+      </c>
+      <c r="P41" s="1">
+        <v>-0.13838249999999999</v>
+      </c>
+      <c r="Q41">
+        <f t="shared" ref="Q41:Q45" si="3">_xlfn.RANK.AVG(P41,P$40:P$45,1)</f>
+        <v>4</v>
+      </c>
+      <c r="R41" s="3">
+        <v>3.6038389999999998</v>
+      </c>
+      <c r="S41">
+        <f t="shared" ref="S41:S45" si="4">_xlfn.RANK.AVG(R41,R$40:R$45,1)</f>
+        <v>5</v>
+      </c>
+      <c r="AC41" s="1">
+        <v>2</v>
+      </c>
+      <c r="AD41" s="1">
+        <v>-0.13281899999999999</v>
+      </c>
+      <c r="AE41">
+        <f t="shared" ref="AE41:AE43" si="5">_xlfn.RANK.AVG(AD41, AD$40:AD$43,1)</f>
+        <v>4</v>
+      </c>
+      <c r="AF41" s="3">
+        <v>2.7827199999999999</v>
+      </c>
+      <c r="AG41">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A42" s="1">
+        <v>3</v>
+      </c>
+      <c r="B42" s="1">
+        <v>-0.14957390000000001</v>
+      </c>
+      <c r="C42">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="D42" s="3">
+        <v>3.6753770000000001</v>
+      </c>
+      <c r="E42">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="O42" s="1">
+        <v>7</v>
+      </c>
+      <c r="P42" s="1">
+        <v>-0.14164119999999999</v>
+      </c>
+      <c r="Q42">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="R42" s="3">
+        <v>2.7476090000000002</v>
+      </c>
+      <c r="S42">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="AC42" s="1">
+        <v>5</v>
+      </c>
+      <c r="AD42" s="1">
+        <v>-0.2662949</v>
+      </c>
+      <c r="AE42">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="AF42" s="3">
+        <v>4.2643740000000001</v>
+      </c>
+      <c r="AG42">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A43" s="1">
+        <v>4</v>
+      </c>
+      <c r="B43" s="1">
+        <v>-0.13838249999999999</v>
+      </c>
+      <c r="C43">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="D43" s="3">
+        <v>3.6038389999999998</v>
+      </c>
+      <c r="E43">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="O43" s="1">
+        <v>8</v>
+      </c>
+      <c r="P43" s="1">
+        <v>-0.13194539999999999</v>
+      </c>
+      <c r="Q43">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="R43" s="3">
+        <v>2.3836249999999999</v>
+      </c>
+      <c r="S43">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AC43" s="1">
+        <v>10</v>
+      </c>
+      <c r="AD43" s="1">
+        <v>-0.15528020000000001</v>
+      </c>
+      <c r="AE43">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="AF43" s="3">
+        <v>2.2407919999999999</v>
+      </c>
+      <c r="AG43">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A44" s="1">
+        <v>5</v>
+      </c>
+      <c r="B44" s="1">
+        <v>-0.2662949</v>
+      </c>
+      <c r="C44">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="D44" s="3">
+        <v>4.2643740000000001</v>
+      </c>
+      <c r="E44">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="O44" s="1">
+        <v>11</v>
+      </c>
+      <c r="P44" s="1">
+        <v>-0.15887780000000001</v>
+      </c>
+      <c r="Q44">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="R44" s="3">
+        <v>2.8338070000000002</v>
+      </c>
+      <c r="S44">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A45" s="1">
+        <v>7</v>
+      </c>
+      <c r="B45" s="1">
+        <v>-0.14164119999999999</v>
+      </c>
+      <c r="C45">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="D45" s="3">
+        <v>2.7476090000000002</v>
+      </c>
+      <c r="E45">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="O45" s="1">
+        <v>12</v>
+      </c>
+      <c r="P45" s="1">
+        <v>-0.137266</v>
+      </c>
+      <c r="Q45">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="R45" s="3">
+        <v>2.4946600000000001</v>
+      </c>
+      <c r="S45">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A46" s="1">
+        <v>8</v>
+      </c>
+      <c r="B46" s="1">
+        <v>-0.13194539999999999</v>
+      </c>
+      <c r="C46">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="D46" s="3">
+        <v>2.3836249999999999</v>
+      </c>
+      <c r="E46">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A47" s="1">
+        <v>10</v>
+      </c>
+      <c r="B47" s="1">
+        <v>-0.15528020000000001</v>
+      </c>
+      <c r="C47">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="D47" s="3">
+        <v>2.2407919999999999</v>
+      </c>
+      <c r="E47">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A48" s="1">
+        <v>11</v>
+      </c>
+      <c r="B48" s="1">
+        <v>-0.15887780000000001</v>
+      </c>
+      <c r="C48">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="D48" s="3">
+        <v>2.8338070000000002</v>
+      </c>
+      <c r="E48">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A49" s="1">
+        <v>12</v>
+      </c>
+      <c r="B49" s="1">
+        <v>-0.137266</v>
+      </c>
+      <c r="C49">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="D49" s="3">
+        <v>2.4946600000000001</v>
+      </c>
+      <c r="E49">
+        <f t="shared" si="2"/>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
